--- a/Industry_Sales_project done.xlsx
+++ b/Industry_Sales_project done.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\Industry sales project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2C07837-AE01-4E60-9E94-2F68BF9DE876}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D151142-14DC-4A15-B2B3-7FBAA0C0CCEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Messy data" sheetId="6" r:id="rId1"/>
-    <sheet name="SalesData" sheetId="2" r:id="rId2"/>
+    <sheet name="Messy Sales data" sheetId="6" r:id="rId1"/>
+    <sheet name="Cleaned SalesData" sheetId="2" r:id="rId2"/>
     <sheet name="Updated Data" sheetId="4" r:id="rId3"/>
     <sheet name="Sorting" sheetId="5" r:id="rId4"/>
     <sheet name="Pivot" sheetId="3" r:id="rId5"/>
@@ -753,6 +753,7 @@
     <xf numFmtId="166" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -766,7 +767,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -889,6 +889,47 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="[$PKR]\ #,##0.0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="[$PKR]\ #,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="[$PKR]\ #,##0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left"/>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="166" formatCode="[$PKR]\ #,##0.0"/>
     </dxf>
     <dxf>
@@ -908,47 +949,6 @@
     </dxf>
     <dxf>
       <alignment horizontal="right"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="[$PKR]\ #,##0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="[$PKR]\ #,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="[$PKR]\ #,##0"/>
     </dxf>
     <dxf>
       <alignment horizontal="right"/>
@@ -8533,6 +8533,341 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0500-000009000000}" name="PivotTable15" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Region">
+  <location ref="K22:L27" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="22">
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField axis="axisRow" showAll="0" sortType="descending">
+      <items count="5">
+        <item x="2"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Returned orders" fld="12" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight17" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable10.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0500-00000A000000}" name="PivotTable9" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Quarter">
+  <location ref="K13:L18" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="22">
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" numFmtId="164" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="16"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name=" Revenue" fld="10" baseField="16" baseItem="1" numFmtId="166"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight17" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable11.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0500-000002000000}" name="PivotTable4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Sales Person">
+  <location ref="H3:I10" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="22">
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="7">
+        <item x="4"/>
+        <item x="5"/>
+        <item x="0"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="3"/>
+  </rowFields>
+  <rowItems count="7">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Quantity" fld="7" baseField="3" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight17" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable12.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0500-00000B000000}" name="PivotTable12" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Region" colHeaderCaption="Category">
+  <location ref="A35:E41" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="22">
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField axis="axisRow" showAll="0" sortType="descending">
+      <items count="5">
+        <item x="2"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="2">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+            <reference field="5" count="1" selected="0">
+              <x v="1"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" numFmtId="164" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="5"/>
+  </colFields>
+  <colItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Region vs Category" fld="10" baseField="2" baseItem="2" numFmtId="166"/>
+  </dataFields>
+  <formats count="1">
+    <format dxfId="21">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight17" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable13.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0500-000000000000}" name="PivotTable13" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Salesperson" colHeaderCaption="Regions">
   <location ref="A48:F56" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="22">
@@ -8636,7 +8971,7 @@
     <dataField name="Revenue calc" fld="10" baseField="3" baseItem="1" numFmtId="166"/>
   </dataFields>
   <formats count="9">
-    <format dxfId="19">
+    <format dxfId="30">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="2" count="3" selected="0">
@@ -8647,10 +8982,10 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="18">
+    <format dxfId="29">
       <pivotArea grandCol="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="17">
+    <format dxfId="28">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="2" count="1" selected="0">
@@ -8659,7 +8994,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="16">
+    <format dxfId="27">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="2" count="1" selected="0">
@@ -8668,7 +9003,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="15">
+    <format dxfId="26">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="2" count="1" selected="0">
@@ -8677,7 +9012,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="14">
+    <format dxfId="25">
       <pivotArea dataOnly="0" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="2" count="1">
@@ -8686,7 +9021,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="13">
+    <format dxfId="24">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="2" count="3">
@@ -8697,10 +9032,10 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="12">
+    <format dxfId="23">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="11">
+    <format dxfId="22">
       <pivotArea outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -8719,416 +9054,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable10.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0500-000006000000}" name="PivotTable14" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Payment method" colHeaderCaption="Region">
-  <location ref="H35:M40" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
-  <pivotFields count="22">
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField axis="axisCol" showAll="0">
-      <items count="5">
-        <item x="2"/>
-        <item x="3"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" numFmtId="164" showAll="0"/>
-    <pivotField axis="axisRow" showAll="0" sortType="descending">
-      <items count="4">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-      <autoSortScope>
-        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
-          <references count="2">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-            <reference field="2" count="1" selected="0">
-              <x v="1"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </autoSortScope>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="11"/>
-  </rowFields>
-  <rowItems count="4">
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="2"/>
-  </colFields>
-  <colItems count="5">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <dataFields count="1">
-    <dataField name=" Revenue" fld="10" baseField="11" baseItem="0" numFmtId="166"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight17" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable11.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0500-000002000000}" name="PivotTable4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Sales Person">
-  <location ref="H3:I10" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="22">
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="7">
-        <item x="4"/>
-        <item x="5"/>
-        <item x="0"/>
-        <item x="3"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="3"/>
-  </rowFields>
-  <rowItems count="7">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Quantity" fld="7" baseField="3" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight17" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable12.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0500-000009000000}" name="PivotTable15" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Region">
-  <location ref="K22:L27" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="22">
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField axis="axisRow" showAll="0" sortType="descending">
-      <items count="5">
-        <item x="2"/>
-        <item x="3"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-      <autoSortScope>
-        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
-          <references count="1">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </autoSortScope>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="2"/>
-  </rowFields>
-  <rowItems count="5">
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Returned orders" fld="12" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight17" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable13.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0500-000007000000}" name="PivotTable7" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Order Status">
-  <location ref="E13:F17" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="22">
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" numFmtId="164" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="12"/>
-  </rowFields>
-  <rowItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Total Revenue" fld="10" baseField="12" baseItem="2" numFmtId="166"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight17" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
 <file path=xl/pivotTables/pivotTable14.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0500-000003000000}" name="PivotTable11" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Category">
-  <location ref="E22:F26" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="22">
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0" sortType="descending">
-      <items count="4">
-        <item x="0"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-      <autoSortScope>
-        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
-          <references count="1">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </autoSortScope>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="5"/>
-  </rowFields>
-  <rowItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Total Quantity" fld="7" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="2">
-    <format dxfId="30">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="29">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight17" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0500-000008000000}" name="PivotTable6" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="8" rowHeaderCaption="Payment method">
   <location ref="A13:B17" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="22">
@@ -9241,6 +9167,93 @@
 </pivotTableDefinition>
 </file>
 
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0500-000001000000}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6" rowHeaderCaption="Region">
+  <location ref="A3:B8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="22">
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField axis="axisRow" showAll="0" sortType="descending">
+      <items count="5">
+        <item x="2"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField dataField="1" numFmtId="164" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of NET Revenue" fld="19" baseField="2" baseItem="1" numFmtId="166"/>
+  </dataFields>
+  <formats count="2">
+    <format dxfId="12">
+      <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="11">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight18" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0500-000005000000}" name="PivotTable10" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Product">
   <location ref="A21:B31" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
@@ -9332,7 +9345,7 @@
     <dataField name="Total Quantity" fld="7" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="20">
+    <format dxfId="13">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="6" count="0"/>
@@ -9350,6 +9363,351 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0500-000007000000}" name="PivotTable7" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Order Status">
+  <location ref="E13:F17" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="22">
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" numFmtId="164" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="12"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Total Revenue" fld="10" baseField="12" baseItem="2" numFmtId="166"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight17" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0500-00000C000000}" name="PivotTable5" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Region">
+  <location ref="K3:L8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="22">
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="5">
+        <item x="2"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" numFmtId="164" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Average Revenue" fld="10" subtotal="average" baseField="2" baseItem="2" numFmtId="166"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight17" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0500-000003000000}" name="PivotTable11" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Category">
+  <location ref="E22:F26" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="22">
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0" sortType="descending">
+      <items count="4">
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="5"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Total Quantity" fld="7" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="2">
+    <format dxfId="15">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="14">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight17" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0500-000004000000}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3" rowHeaderCaption="Category" colHeaderCaption="Product">
+  <location ref="E3:F7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="22">
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="4">
+        <item sd="0" x="0"/>
+        <item sd="0" x="2"/>
+        <item sd="0" x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="10">
+        <item x="3"/>
+        <item x="4"/>
+        <item x="1"/>
+        <item x="5"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item x="8"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" numFmtId="164" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="2">
+    <field x="5"/>
+    <field x="6"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Revenue " fld="10" baseField="5" baseItem="2" numFmtId="166"/>
+  </dataFields>
+  <formats count="5">
+    <format dxfId="20">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="5" count="1">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="19">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="5" count="1">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="18">
+      <pivotArea outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="17">
+      <pivotArea field="5" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="16">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="1">
+    <chartFormat chart="2" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight17" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0500-00000D000000}" name="PivotTable8" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7" rowHeaderCaption="Month">
   <location ref="H13:I26" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="22">
@@ -9460,278 +9818,13 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0500-00000A000000}" name="PivotTable9" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Quarter">
-  <location ref="K13:L18" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+<file path=xl/pivotTables/pivotTable9.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0500-000006000000}" name="PivotTable14" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Payment method" colHeaderCaption="Region">
+  <location ref="H35:M40" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="22">
     <pivotField showAll="0"/>
     <pivotField numFmtId="14" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" numFmtId="164" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="5">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="16"/>
-  </rowFields>
-  <rowItems count="5">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name=" Revenue" fld="10" baseField="16" baseItem="1" numFmtId="166"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight17" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0500-00000B000000}" name="PivotTable12" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Region" colHeaderCaption="Category">
-  <location ref="A35:E41" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
-  <pivotFields count="22">
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField axis="axisRow" showAll="0" sortType="descending">
-      <items count="5">
-        <item x="2"/>
-        <item x="3"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-      <autoSortScope>
-        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
-          <references count="2">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-            <reference field="5" count="1" selected="0">
-              <x v="1"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </autoSortScope>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
     <pivotField axis="axisCol" showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" numFmtId="164" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="2"/>
-  </rowFields>
-  <rowItems count="5">
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="5"/>
-  </colFields>
-  <colItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Region vs Category" fld="10" baseField="2" baseItem="2" numFmtId="166"/>
-  </dataFields>
-  <formats count="1">
-    <format dxfId="21">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight17" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0500-000001000000}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6" rowHeaderCaption="Region">
-  <location ref="A3:B8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="22">
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField axis="axisRow" showAll="0" sortType="descending">
-      <items count="5">
-        <item x="2"/>
-        <item x="3"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-      <autoSortScope>
-        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
-          <references count="1">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </autoSortScope>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField dataField="1" numFmtId="164" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="2"/>
-  </rowFields>
-  <rowItems count="5">
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of NET Revenue" fld="19" baseField="2" baseItem="1" numFmtId="166"/>
-  </dataFields>
-  <formats count="2">
-    <format dxfId="23">
-      <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="22">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight18" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0500-00000C000000}" name="PivotTable5" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Region">
-  <location ref="K3:L8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="22">
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
       <items count="5">
         <item x="2"/>
         <item x="3"/>
@@ -9748,7 +9841,26 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField dataField="1" numFmtId="164" showAll="0"/>
-    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0" sortType="descending">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="2">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+            <reference field="2" count="1" selected="0">
+              <x v="1"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
     <pivotField showAll="0"/>
     <pivotField numFmtId="164" showAll="0"/>
     <pivotField showAll="0"/>
@@ -9761,9 +9873,26 @@
     <pivotField showAll="0"/>
   </pivotFields>
   <rowFields count="1">
+    <field x="11"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
     <field x="2"/>
-  </rowFields>
-  <rowItems count="5">
+  </colFields>
+  <colItems count="5">
     <i>
       <x/>
     </i>
@@ -9779,139 +9908,10 @@
     <i t="grand">
       <x/>
     </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
   </colItems>
   <dataFields count="1">
-    <dataField name="Average Revenue" fld="10" subtotal="average" baseField="2" baseItem="2" numFmtId="166"/>
+    <dataField name=" Revenue" fld="10" baseField="11" baseItem="0" numFmtId="166"/>
   </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight17" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable9.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0500-000004000000}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3" rowHeaderCaption="Category" colHeaderCaption="Product">
-  <location ref="E3:F7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="22">
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="4">
-        <item sd="0" x="0"/>
-        <item sd="0" x="2"/>
-        <item sd="0" x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="10">
-        <item x="3"/>
-        <item x="4"/>
-        <item x="1"/>
-        <item x="5"/>
-        <item x="0"/>
-        <item x="2"/>
-        <item x="8"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" numFmtId="164" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="2">
-    <field x="5"/>
-    <field x="6"/>
-  </rowFields>
-  <rowItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Revenue " fld="10" baseField="5" baseItem="2" numFmtId="166"/>
-  </dataFields>
-  <formats count="5">
-    <format dxfId="28">
-      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
-        <references count="1">
-          <reference field="5" count="1">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="27">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="5" count="1">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="26">
-      <pivotArea outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="25">
-      <pivotArea field="5" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="24">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-  </formats>
-  <chartFormats count="1">
-    <chartFormat chart="2" format="1" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
   <pivotTableStyleInfo name="PivotStyleLight17" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
@@ -10358,7 +10358,7 @@
       <c r="A2" s="18">
         <v>1001</v>
       </c>
-      <c r="B2" s="32">
+      <c r="B2" s="27">
         <v>46146</v>
       </c>
       <c r="C2" s="18" t="s">
@@ -10399,7 +10399,7 @@
       <c r="A3" s="18">
         <v>1002</v>
       </c>
-      <c r="B3" s="32">
+      <c r="B3" s="27">
         <v>45817</v>
       </c>
       <c r="C3" s="18" t="s">
@@ -10440,7 +10440,7 @@
       <c r="A4" s="18">
         <v>1003</v>
       </c>
-      <c r="B4" s="32">
+      <c r="B4" s="27">
         <v>45897</v>
       </c>
       <c r="C4" s="18" t="s">
@@ -10481,7 +10481,7 @@
       <c r="A5" s="18">
         <v>1004</v>
       </c>
-      <c r="B5" s="32">
+      <c r="B5" s="27">
         <v>46159</v>
       </c>
       <c r="C5" s="18" t="s">
@@ -10522,7 +10522,7 @@
       <c r="A6" s="18">
         <v>1005</v>
       </c>
-      <c r="B6" s="32">
+      <c r="B6" s="27">
         <v>46180</v>
       </c>
       <c r="C6" s="18" t="s">
@@ -10563,7 +10563,7 @@
       <c r="A7" s="18">
         <v>1006</v>
       </c>
-      <c r="B7" s="32">
+      <c r="B7" s="27">
         <v>46104</v>
       </c>
       <c r="C7" s="18" t="s">
@@ -10604,7 +10604,7 @@
       <c r="A8" s="18">
         <v>1007</v>
       </c>
-      <c r="B8" s="32">
+      <c r="B8" s="27">
         <v>45916</v>
       </c>
       <c r="C8" s="18" t="s">
@@ -10645,7 +10645,7 @@
       <c r="A9" s="18">
         <v>1008</v>
       </c>
-      <c r="B9" s="32">
+      <c r="B9" s="27">
         <v>46103</v>
       </c>
       <c r="C9" s="18" t="s">
@@ -10686,7 +10686,7 @@
       <c r="A10" s="18">
         <v>1009</v>
       </c>
-      <c r="B10" s="32">
+      <c r="B10" s="27">
         <v>46026</v>
       </c>
       <c r="C10" s="18" t="s">
@@ -10727,7 +10727,7 @@
       <c r="A11" s="18">
         <v>1010</v>
       </c>
-      <c r="B11" s="32">
+      <c r="B11" s="27">
         <v>45771</v>
       </c>
       <c r="C11" s="18" t="s">
@@ -10768,7 +10768,7 @@
       <c r="A12" s="18">
         <v>1011</v>
       </c>
-      <c r="B12" s="32">
+      <c r="B12" s="27">
         <v>46059</v>
       </c>
       <c r="C12" s="18" t="s">
@@ -10809,7 +10809,7 @@
       <c r="A13" s="18">
         <v>1012</v>
       </c>
-      <c r="B13" s="32">
+      <c r="B13" s="27">
         <v>46175</v>
       </c>
       <c r="C13" s="18" t="s">
@@ -10850,7 +10850,7 @@
       <c r="A14" s="18">
         <v>1013</v>
       </c>
-      <c r="B14" s="32">
+      <c r="B14" s="27">
         <v>46181</v>
       </c>
       <c r="C14" s="18" t="s">
@@ -10891,7 +10891,7 @@
       <c r="A15" s="18">
         <v>1014</v>
       </c>
-      <c r="B15" s="32">
+      <c r="B15" s="27">
         <v>46080</v>
       </c>
       <c r="C15" s="18" t="s">
@@ -10932,7 +10932,7 @@
       <c r="A16" s="18">
         <v>1015</v>
       </c>
-      <c r="B16" s="32">
+      <c r="B16" s="27">
         <v>45920</v>
       </c>
       <c r="C16" s="18" t="s">
@@ -10973,7 +10973,7 @@
       <c r="A17" s="18">
         <v>1016</v>
       </c>
-      <c r="B17" s="32">
+      <c r="B17" s="27">
         <v>46050</v>
       </c>
       <c r="C17" s="18" t="s">
@@ -11014,7 +11014,7 @@
       <c r="A18" s="18">
         <v>1017</v>
       </c>
-      <c r="B18" s="32">
+      <c r="B18" s="27">
         <v>45712</v>
       </c>
       <c r="C18" s="18" t="s">
@@ -11055,7 +11055,7 @@
       <c r="A19" s="18">
         <v>1018</v>
       </c>
-      <c r="B19" s="32">
+      <c r="B19" s="27">
         <v>45698</v>
       </c>
       <c r="C19" s="18" t="s">
@@ -11096,7 +11096,7 @@
       <c r="A20" s="18">
         <v>1019</v>
       </c>
-      <c r="B20" s="32">
+      <c r="B20" s="27">
         <v>45874</v>
       </c>
       <c r="C20" s="18" t="s">
@@ -11137,7 +11137,7 @@
       <c r="A21" s="18">
         <v>1020</v>
       </c>
-      <c r="B21" s="32">
+      <c r="B21" s="27">
         <v>45723</v>
       </c>
       <c r="C21" s="18" t="s">
@@ -11178,7 +11178,7 @@
       <c r="A22" s="18">
         <v>1021</v>
       </c>
-      <c r="B22" s="32">
+      <c r="B22" s="27">
         <v>45875</v>
       </c>
       <c r="C22" s="18" t="s">
@@ -11219,7 +11219,7 @@
       <c r="A23" s="18">
         <v>1022</v>
       </c>
-      <c r="B23" s="32">
+      <c r="B23" s="27">
         <v>45965</v>
       </c>
       <c r="C23" s="18" t="s">
@@ -11260,7 +11260,7 @@
       <c r="A24" s="18">
         <v>1023</v>
       </c>
-      <c r="B24" s="32">
+      <c r="B24" s="27">
         <v>45966</v>
       </c>
       <c r="C24" s="18" t="s">
@@ -11301,7 +11301,7 @@
       <c r="A25" s="18">
         <v>1024</v>
       </c>
-      <c r="B25" s="32">
+      <c r="B25" s="27">
         <v>45720</v>
       </c>
       <c r="C25" s="18" t="s">
@@ -11342,7 +11342,7 @@
       <c r="A26" s="18">
         <v>1025</v>
       </c>
-      <c r="B26" s="32">
+      <c r="B26" s="27">
         <v>45791</v>
       </c>
       <c r="C26" s="18" t="s">
@@ -11383,7 +11383,7 @@
       <c r="A27" s="18">
         <v>1026</v>
       </c>
-      <c r="B27" s="32">
+      <c r="B27" s="27">
         <v>45670</v>
       </c>
       <c r="C27" s="18" t="s">
@@ -11424,7 +11424,7 @@
       <c r="A28" s="18">
         <v>1027</v>
       </c>
-      <c r="B28" s="32">
+      <c r="B28" s="27">
         <v>46195</v>
       </c>
       <c r="C28" s="18" t="s">
@@ -11465,7 +11465,7 @@
       <c r="A29" s="18">
         <v>1028</v>
       </c>
-      <c r="B29" s="32">
+      <c r="B29" s="27">
         <v>45775</v>
       </c>
       <c r="C29" s="18" t="s">
@@ -11506,7 +11506,7 @@
       <c r="A30" s="18">
         <v>1029</v>
       </c>
-      <c r="B30" s="32">
+      <c r="B30" s="27">
         <v>46144</v>
       </c>
       <c r="C30" s="18" t="s">
@@ -11545,7 +11545,7 @@
       <c r="A31" s="18">
         <v>1030</v>
       </c>
-      <c r="B31" s="32">
+      <c r="B31" s="27">
         <v>45849</v>
       </c>
       <c r="C31" s="18" t="s">
@@ -11586,7 +11586,7 @@
       <c r="A32" s="18">
         <v>1031</v>
       </c>
-      <c r="B32" s="32">
+      <c r="B32" s="27">
         <v>46114</v>
       </c>
       <c r="C32" s="18" t="s">
@@ -11627,7 +11627,7 @@
       <c r="A33" s="18">
         <v>1032</v>
       </c>
-      <c r="B33" s="32">
+      <c r="B33" s="27">
         <v>45986</v>
       </c>
       <c r="C33" s="18" t="s">
@@ -11668,7 +11668,7 @@
       <c r="A34" s="18">
         <v>1033</v>
       </c>
-      <c r="B34" s="32">
+      <c r="B34" s="27">
         <v>45763</v>
       </c>
       <c r="C34" s="18" t="s">
@@ -11709,7 +11709,7 @@
       <c r="A35" s="18">
         <v>1034</v>
       </c>
-      <c r="B35" s="32">
+      <c r="B35" s="27">
         <v>46097</v>
       </c>
       <c r="C35" s="18" t="s">
@@ -11750,7 +11750,7 @@
       <c r="A36" s="18">
         <v>1035</v>
       </c>
-      <c r="B36" s="32">
+      <c r="B36" s="27">
         <v>46144</v>
       </c>
       <c r="C36" s="18" t="s">
@@ -11791,7 +11791,7 @@
       <c r="A37" s="18">
         <v>1036</v>
       </c>
-      <c r="B37" s="32">
+      <c r="B37" s="27">
         <v>45862</v>
       </c>
       <c r="C37" s="18" t="s">
@@ -11832,7 +11832,7 @@
       <c r="A38" s="18">
         <v>1037</v>
       </c>
-      <c r="B38" s="32">
+      <c r="B38" s="27">
         <v>45864</v>
       </c>
       <c r="C38" s="18" t="s">
@@ -11873,7 +11873,7 @@
       <c r="A39" s="18">
         <v>1038</v>
       </c>
-      <c r="B39" s="32">
+      <c r="B39" s="27">
         <v>45942</v>
       </c>
       <c r="C39" s="18" t="s">
@@ -11914,7 +11914,7 @@
       <c r="A40" s="18">
         <v>1039</v>
       </c>
-      <c r="B40" s="32">
+      <c r="B40" s="27">
         <v>45777</v>
       </c>
       <c r="C40" s="18" t="s">
@@ -11955,7 +11955,7 @@
       <c r="A41" s="18">
         <v>1040</v>
       </c>
-      <c r="B41" s="32">
+      <c r="B41" s="27">
         <v>45939</v>
       </c>
       <c r="C41" s="18" t="s">
@@ -11996,7 +11996,7 @@
       <c r="A42" s="18">
         <v>1041</v>
       </c>
-      <c r="B42" s="32">
+      <c r="B42" s="27">
         <v>46031</v>
       </c>
       <c r="C42" s="18" t="s">
@@ -12037,7 +12037,7 @@
       <c r="A43" s="18">
         <v>1042</v>
       </c>
-      <c r="B43" s="32">
+      <c r="B43" s="27">
         <v>46188</v>
       </c>
       <c r="C43" s="18" t="s">
@@ -12078,7 +12078,7 @@
       <c r="A44" s="18">
         <v>1043</v>
       </c>
-      <c r="B44" s="32">
+      <c r="B44" s="27">
         <v>46145</v>
       </c>
       <c r="C44" s="18" t="s">
@@ -12119,7 +12119,7 @@
       <c r="A45" s="18">
         <v>1044</v>
       </c>
-      <c r="B45" s="32">
+      <c r="B45" s="27">
         <v>45658</v>
       </c>
       <c r="C45" s="18" t="s">
@@ -12160,7 +12160,7 @@
       <c r="A46" s="18">
         <v>1045</v>
       </c>
-      <c r="B46" s="32">
+      <c r="B46" s="27">
         <v>45872</v>
       </c>
       <c r="C46" s="18" t="s">
@@ -12201,7 +12201,7 @@
       <c r="A47" s="18">
         <v>1046</v>
       </c>
-      <c r="B47" s="32">
+      <c r="B47" s="27">
         <v>45739</v>
       </c>
       <c r="C47" s="18" t="s">
@@ -12242,7 +12242,7 @@
       <c r="A48" s="18">
         <v>1047</v>
       </c>
-      <c r="B48" s="32">
+      <c r="B48" s="27">
         <v>45895</v>
       </c>
       <c r="C48" s="18" t="s">
@@ -12283,7 +12283,7 @@
       <c r="A49" s="18">
         <v>1048</v>
       </c>
-      <c r="B49" s="32">
+      <c r="B49" s="27">
         <v>45769</v>
       </c>
       <c r="C49" s="18" t="s">
@@ -12324,7 +12324,7 @@
       <c r="A50" s="18">
         <v>1049</v>
       </c>
-      <c r="B50" s="32">
+      <c r="B50" s="27">
         <v>46198</v>
       </c>
       <c r="C50" s="18" t="s">
@@ -12365,7 +12365,7 @@
       <c r="A51" s="18">
         <v>1050</v>
       </c>
-      <c r="B51" s="32">
+      <c r="B51" s="27">
         <v>45742</v>
       </c>
       <c r="C51" s="18" t="s">
@@ -12406,7 +12406,7 @@
       <c r="A52" s="18">
         <v>1051</v>
       </c>
-      <c r="B52" s="32">
+      <c r="B52" s="27">
         <v>45683</v>
       </c>
       <c r="C52" s="18" t="s">
@@ -12447,7 +12447,7 @@
       <c r="A53" s="18">
         <v>1052</v>
       </c>
-      <c r="B53" s="32">
+      <c r="B53" s="27">
         <v>45751</v>
       </c>
       <c r="C53" s="18" t="s">
@@ -12488,7 +12488,7 @@
       <c r="A54" s="18">
         <v>1053</v>
       </c>
-      <c r="B54" s="32">
+      <c r="B54" s="27">
         <v>46122</v>
       </c>
       <c r="C54" s="18" t="s">
@@ -12529,7 +12529,7 @@
       <c r="A55" s="18">
         <v>1054</v>
       </c>
-      <c r="B55" s="32">
+      <c r="B55" s="27">
         <v>45791</v>
       </c>
       <c r="C55" s="18" t="s">
@@ -12570,7 +12570,7 @@
       <c r="A56" s="18">
         <v>1055</v>
       </c>
-      <c r="B56" s="32">
+      <c r="B56" s="27">
         <v>46126</v>
       </c>
       <c r="C56" s="18" t="s">
@@ -12611,7 +12611,7 @@
       <c r="A57" s="18">
         <v>1056</v>
       </c>
-      <c r="B57" s="32">
+      <c r="B57" s="27">
         <v>45998</v>
       </c>
       <c r="C57" s="18" t="s">
@@ -12652,7 +12652,7 @@
       <c r="A58" s="18">
         <v>1057</v>
       </c>
-      <c r="B58" s="32">
+      <c r="B58" s="27">
         <v>46014</v>
       </c>
       <c r="C58" s="18" t="s">
@@ -12693,7 +12693,7 @@
       <c r="A59" s="18">
         <v>1058</v>
       </c>
-      <c r="B59" s="32">
+      <c r="B59" s="27">
         <v>45980</v>
       </c>
       <c r="C59" s="18" t="s">
@@ -12734,7 +12734,7 @@
       <c r="A60" s="18">
         <v>1059</v>
       </c>
-      <c r="B60" s="32">
+      <c r="B60" s="27">
         <v>45694</v>
       </c>
       <c r="C60" s="18" t="s">
@@ -12775,7 +12775,7 @@
       <c r="A61" s="18">
         <v>1060</v>
       </c>
-      <c r="B61" s="32">
+      <c r="B61" s="27">
         <v>45711</v>
       </c>
       <c r="C61" s="18" t="s">
@@ -12816,7 +12816,7 @@
       <c r="A62" s="18">
         <v>1061</v>
       </c>
-      <c r="B62" s="32">
+      <c r="B62" s="27">
         <v>45703</v>
       </c>
       <c r="C62" s="18" t="s">
@@ -12857,7 +12857,7 @@
       <c r="A63" s="18">
         <v>1062</v>
       </c>
-      <c r="B63" s="32">
+      <c r="B63" s="27">
         <v>45864</v>
       </c>
       <c r="C63" s="18" t="s">
@@ -12898,7 +12898,7 @@
       <c r="A64" s="18">
         <v>1063</v>
       </c>
-      <c r="B64" s="32">
+      <c r="B64" s="27">
         <v>45764</v>
       </c>
       <c r="C64" s="18" t="s">
@@ -12939,7 +12939,7 @@
       <c r="A65" s="18">
         <v>1064</v>
       </c>
-      <c r="B65" s="32">
+      <c r="B65" s="27">
         <v>45867</v>
       </c>
       <c r="C65" s="18" t="s">
@@ -12980,7 +12980,7 @@
       <c r="A66" s="18">
         <v>1065</v>
       </c>
-      <c r="B66" s="32">
+      <c r="B66" s="27">
         <v>46015</v>
       </c>
       <c r="C66" s="18" t="s">
@@ -13021,7 +13021,7 @@
       <c r="A67" s="18">
         <v>1066</v>
       </c>
-      <c r="B67" s="32">
+      <c r="B67" s="27">
         <v>45861</v>
       </c>
       <c r="C67" s="18" t="s">
@@ -13062,7 +13062,7 @@
       <c r="A68" s="18">
         <v>1067</v>
       </c>
-      <c r="B68" s="32">
+      <c r="B68" s="27">
         <v>45933</v>
       </c>
       <c r="C68" s="18" t="s">
@@ -13103,7 +13103,7 @@
       <c r="A69" s="18">
         <v>1068</v>
       </c>
-      <c r="B69" s="32">
+      <c r="B69" s="27">
         <v>45796</v>
       </c>
       <c r="C69" s="18" t="s">
@@ -13144,7 +13144,7 @@
       <c r="A70" s="18">
         <v>1069</v>
       </c>
-      <c r="B70" s="32">
+      <c r="B70" s="27">
         <v>45674</v>
       </c>
       <c r="C70" s="18" t="s">
@@ -13185,7 +13185,7 @@
       <c r="A71" s="18">
         <v>1070</v>
       </c>
-      <c r="B71" s="32">
+      <c r="B71" s="27">
         <v>46003</v>
       </c>
       <c r="C71" s="18" t="s">
@@ -13226,7 +13226,7 @@
       <c r="A72" s="18">
         <v>1071</v>
       </c>
-      <c r="B72" s="32">
+      <c r="B72" s="27">
         <v>45669</v>
       </c>
       <c r="C72" s="18" t="s">
@@ -13267,7 +13267,7 @@
       <c r="A73" s="18">
         <v>1072</v>
       </c>
-      <c r="B73" s="32">
+      <c r="B73" s="27">
         <v>45858</v>
       </c>
       <c r="C73" s="18" t="s">
@@ -13308,7 +13308,7 @@
       <c r="A74" s="18">
         <v>1073</v>
       </c>
-      <c r="B74" s="32">
+      <c r="B74" s="27">
         <v>45891</v>
       </c>
       <c r="C74" s="18" t="s">
@@ -13349,7 +13349,7 @@
       <c r="A75" s="18">
         <v>1074</v>
       </c>
-      <c r="B75" s="32">
+      <c r="B75" s="27">
         <v>46141</v>
       </c>
       <c r="C75" s="18" t="s">
@@ -13390,7 +13390,7 @@
       <c r="A76" s="18">
         <v>1075</v>
       </c>
-      <c r="B76" s="32">
+      <c r="B76" s="27">
         <v>45831</v>
       </c>
       <c r="C76" s="18" t="s">
@@ -13431,7 +13431,7 @@
       <c r="A77" s="18">
         <v>1076</v>
       </c>
-      <c r="B77" s="32">
+      <c r="B77" s="27">
         <v>45968</v>
       </c>
       <c r="C77" s="18" t="s">
@@ -13472,7 +13472,7 @@
       <c r="A78" s="18">
         <v>1077</v>
       </c>
-      <c r="B78" s="32">
+      <c r="B78" s="27">
         <v>46032</v>
       </c>
       <c r="C78" s="18" t="s">
@@ -13513,7 +13513,7 @@
       <c r="A79" s="18">
         <v>1078</v>
       </c>
-      <c r="B79" s="32">
+      <c r="B79" s="27">
         <v>45677</v>
       </c>
       <c r="C79" s="18" t="s">
@@ -13554,7 +13554,7 @@
       <c r="A80" s="18">
         <v>1079</v>
       </c>
-      <c r="B80" s="32">
+      <c r="B80" s="27">
         <v>46061</v>
       </c>
       <c r="C80" s="18" t="s">
@@ -13595,7 +13595,7 @@
       <c r="A81" s="18">
         <v>1080</v>
       </c>
-      <c r="B81" s="32">
+      <c r="B81" s="27">
         <v>45757</v>
       </c>
       <c r="C81" s="18" t="s">
@@ -13636,7 +13636,7 @@
       <c r="A82" s="18">
         <v>1081</v>
       </c>
-      <c r="B82" s="32">
+      <c r="B82" s="27">
         <v>46094</v>
       </c>
       <c r="C82" s="18" t="s">
@@ -13677,7 +13677,7 @@
       <c r="A83" s="18">
         <v>1082</v>
       </c>
-      <c r="B83" s="32">
+      <c r="B83" s="27">
         <v>45964</v>
       </c>
       <c r="C83" s="18" t="s">
@@ -13718,7 +13718,7 @@
       <c r="A84" s="18">
         <v>1083</v>
       </c>
-      <c r="B84" s="32">
+      <c r="B84" s="27">
         <v>46187</v>
       </c>
       <c r="C84" s="18" t="s">
@@ -13759,7 +13759,7 @@
       <c r="A85" s="18">
         <v>1084</v>
       </c>
-      <c r="B85" s="32">
+      <c r="B85" s="27">
         <v>46075</v>
       </c>
       <c r="C85" s="18" t="s">
@@ -13800,7 +13800,7 @@
       <c r="A86" s="18">
         <v>1085</v>
       </c>
-      <c r="B86" s="32">
+      <c r="B86" s="27">
         <v>45911</v>
       </c>
       <c r="C86" s="18" t="s">
@@ -13841,7 +13841,7 @@
       <c r="A87" s="18">
         <v>1086</v>
       </c>
-      <c r="B87" s="32">
+      <c r="B87" s="27">
         <v>45857</v>
       </c>
       <c r="C87" s="18" t="s">
@@ -13882,7 +13882,7 @@
       <c r="A88" s="18">
         <v>1087</v>
       </c>
-      <c r="B88" s="32">
+      <c r="B88" s="27">
         <v>46081</v>
       </c>
       <c r="C88" s="18" t="s">
@@ -13923,7 +13923,7 @@
       <c r="A89" s="18">
         <v>1088</v>
       </c>
-      <c r="B89" s="32">
+      <c r="B89" s="27">
         <v>45765</v>
       </c>
       <c r="C89" s="18" t="s">
@@ -13964,7 +13964,7 @@
       <c r="A90" s="18">
         <v>1089</v>
       </c>
-      <c r="B90" s="32">
+      <c r="B90" s="27">
         <v>45975</v>
       </c>
       <c r="C90" s="18" t="s">
@@ -14005,7 +14005,7 @@
       <c r="A91" s="18">
         <v>1090</v>
       </c>
-      <c r="B91" s="32">
+      <c r="B91" s="27">
         <v>45675</v>
       </c>
       <c r="C91" s="18" t="s">
@@ -14046,7 +14046,7 @@
       <c r="A92" s="18">
         <v>1091</v>
       </c>
-      <c r="B92" s="32">
+      <c r="B92" s="27">
         <v>45842</v>
       </c>
       <c r="C92" s="18" t="s">
@@ -14087,7 +14087,7 @@
       <c r="A93" s="18">
         <v>1092</v>
       </c>
-      <c r="B93" s="32">
+      <c r="B93" s="27">
         <v>46083</v>
       </c>
       <c r="C93" s="18" t="s">
@@ -14128,7 +14128,7 @@
       <c r="A94" s="18">
         <v>1093</v>
       </c>
-      <c r="B94" s="32">
+      <c r="B94" s="27">
         <v>45821</v>
       </c>
       <c r="C94" s="18" t="s">
@@ -14169,7 +14169,7 @@
       <c r="A95" s="18">
         <v>1094</v>
       </c>
-      <c r="B95" s="32">
+      <c r="B95" s="27">
         <v>46011</v>
       </c>
       <c r="C95" s="18" t="s">
@@ -14210,7 +14210,7 @@
       <c r="A96" s="18">
         <v>1095</v>
       </c>
-      <c r="B96" s="32">
+      <c r="B96" s="27">
         <v>45738</v>
       </c>
       <c r="C96" s="18" t="s">
@@ -14251,7 +14251,7 @@
       <c r="A97" s="18">
         <v>1096</v>
       </c>
-      <c r="B97" s="32">
+      <c r="B97" s="27">
         <v>45747</v>
       </c>
       <c r="C97" s="18" t="s">
@@ -14292,7 +14292,7 @@
       <c r="A98" s="18">
         <v>1097</v>
       </c>
-      <c r="B98" s="32">
+      <c r="B98" s="27">
         <v>46025</v>
       </c>
       <c r="C98" s="18" t="s">
@@ -14333,7 +14333,7 @@
       <c r="A99" s="18">
         <v>1098</v>
       </c>
-      <c r="B99" s="32">
+      <c r="B99" s="27">
         <v>45781</v>
       </c>
       <c r="C99" s="18" t="s">
@@ -14374,7 +14374,7 @@
       <c r="A100" s="18">
         <v>1099</v>
       </c>
-      <c r="B100" s="32">
+      <c r="B100" s="27">
         <v>45823</v>
       </c>
       <c r="C100" s="18" t="s">
@@ -14415,7 +14415,7 @@
       <c r="A101" s="18">
         <v>1100</v>
       </c>
-      <c r="B101" s="32">
+      <c r="B101" s="27">
         <v>45739</v>
       </c>
       <c r="C101" s="18" t="s">
@@ -14456,7 +14456,7 @@
       <c r="A102" s="18">
         <v>1101</v>
       </c>
-      <c r="B102" s="32">
+      <c r="B102" s="27">
         <v>45759</v>
       </c>
       <c r="C102" s="18" t="s">
@@ -14497,7 +14497,7 @@
       <c r="A103" s="18">
         <v>1102</v>
       </c>
-      <c r="B103" s="32">
+      <c r="B103" s="27">
         <v>45745</v>
       </c>
       <c r="C103" s="18" t="s">
@@ -14538,7 +14538,7 @@
       <c r="A104" s="18">
         <v>1103</v>
       </c>
-      <c r="B104" s="32">
+      <c r="B104" s="27">
         <v>46070</v>
       </c>
       <c r="C104" s="18" t="s">
@@ -14579,7 +14579,7 @@
       <c r="A105" s="18">
         <v>1104</v>
       </c>
-      <c r="B105" s="32">
+      <c r="B105" s="27">
         <v>45822</v>
       </c>
       <c r="C105" s="18" t="s">
@@ -14620,7 +14620,7 @@
       <c r="A106" s="18">
         <v>1105</v>
       </c>
-      <c r="B106" s="32">
+      <c r="B106" s="27">
         <v>45940</v>
       </c>
       <c r="C106" s="18" t="s">
@@ -14661,7 +14661,7 @@
       <c r="A107" s="18">
         <v>1106</v>
       </c>
-      <c r="B107" s="32">
+      <c r="B107" s="27">
         <v>46196</v>
       </c>
       <c r="C107" s="18" t="s">
@@ -14702,7 +14702,7 @@
       <c r="A108" s="18">
         <v>1107</v>
       </c>
-      <c r="B108" s="32">
+      <c r="B108" s="27">
         <v>45757</v>
       </c>
       <c r="C108" s="18" t="s">
@@ -14743,7 +14743,7 @@
       <c r="A109" s="18">
         <v>1108</v>
       </c>
-      <c r="B109" s="32">
+      <c r="B109" s="27">
         <v>45849</v>
       </c>
       <c r="C109" s="18" t="s">
@@ -14784,7 +14784,7 @@
       <c r="A110" s="18">
         <v>1109</v>
       </c>
-      <c r="B110" s="32">
+      <c r="B110" s="27">
         <v>45809</v>
       </c>
       <c r="C110" s="18" t="s">
@@ -14825,7 +14825,7 @@
       <c r="A111" s="18">
         <v>1110</v>
       </c>
-      <c r="B111" s="32">
+      <c r="B111" s="27">
         <v>46115</v>
       </c>
       <c r="C111" s="18" t="s">
@@ -14866,7 +14866,7 @@
       <c r="A112" s="18">
         <v>1111</v>
       </c>
-      <c r="B112" s="32">
+      <c r="B112" s="27">
         <v>45876</v>
       </c>
       <c r="C112" s="18" t="s">
@@ -14907,7 +14907,7 @@
       <c r="A113" s="18">
         <v>1112</v>
       </c>
-      <c r="B113" s="32">
+      <c r="B113" s="27">
         <v>46109</v>
       </c>
       <c r="C113" s="18" t="s">
@@ -14948,7 +14948,7 @@
       <c r="A114" s="18">
         <v>1113</v>
       </c>
-      <c r="B114" s="32">
+      <c r="B114" s="27">
         <v>45713</v>
       </c>
       <c r="C114" s="18" t="s">
@@ -14989,7 +14989,7 @@
       <c r="A115" s="18">
         <v>1114</v>
       </c>
-      <c r="B115" s="32">
+      <c r="B115" s="27">
         <v>45881</v>
       </c>
       <c r="C115" s="18" t="s">
@@ -15030,7 +15030,7 @@
       <c r="A116" s="18">
         <v>1115</v>
       </c>
-      <c r="B116" s="32">
+      <c r="B116" s="27">
         <v>45689</v>
       </c>
       <c r="C116" s="18" t="s">
@@ -15071,7 +15071,7 @@
       <c r="A117" s="18">
         <v>1116</v>
       </c>
-      <c r="B117" s="32">
+      <c r="B117" s="27">
         <v>45718</v>
       </c>
       <c r="C117" s="18" t="s">
@@ -15112,7 +15112,7 @@
       <c r="A118" s="18">
         <v>1117</v>
       </c>
-      <c r="B118" s="32">
+      <c r="B118" s="27">
         <v>45775</v>
       </c>
       <c r="C118" s="18" t="s">
@@ -15153,7 +15153,7 @@
       <c r="A119" s="18">
         <v>1118</v>
       </c>
-      <c r="B119" s="32">
+      <c r="B119" s="27">
         <v>45916</v>
       </c>
       <c r="C119" s="18" t="s">
@@ -15194,7 +15194,7 @@
       <c r="A120" s="18">
         <v>1119</v>
       </c>
-      <c r="B120" s="32">
+      <c r="B120" s="27">
         <v>45794</v>
       </c>
       <c r="C120" s="18" t="s">
@@ -15235,7 +15235,7 @@
       <c r="A121" s="18">
         <v>1120</v>
       </c>
-      <c r="B121" s="32">
+      <c r="B121" s="27">
         <v>45824</v>
       </c>
       <c r="C121" s="18" t="s">
@@ -15276,7 +15276,7 @@
       <c r="A122" s="18">
         <v>1121</v>
       </c>
-      <c r="B122" s="32">
+      <c r="B122" s="27">
         <v>46032</v>
       </c>
       <c r="C122" s="18" t="s">
@@ -15317,7 +15317,7 @@
       <c r="A123" s="18">
         <v>1122</v>
       </c>
-      <c r="B123" s="32">
+      <c r="B123" s="27">
         <v>46000</v>
       </c>
       <c r="C123" s="18" t="s">
@@ -15358,7 +15358,7 @@
       <c r="A124" s="18">
         <v>1123</v>
       </c>
-      <c r="B124" s="32">
+      <c r="B124" s="27">
         <v>46163</v>
       </c>
       <c r="C124" s="18" t="s">
@@ -15399,7 +15399,7 @@
       <c r="A125" s="18">
         <v>1124</v>
       </c>
-      <c r="B125" s="32">
+      <c r="B125" s="27">
         <v>45805</v>
       </c>
       <c r="C125" s="18" t="s">
@@ -15440,7 +15440,7 @@
       <c r="A126" s="18">
         <v>1125</v>
       </c>
-      <c r="B126" s="32">
+      <c r="B126" s="27">
         <v>46098</v>
       </c>
       <c r="C126" s="18" t="s">
@@ -15481,7 +15481,7 @@
       <c r="A127" s="18">
         <v>1126</v>
       </c>
-      <c r="B127" s="32">
+      <c r="B127" s="27">
         <v>46075</v>
       </c>
       <c r="C127" s="18" t="s">
@@ -15522,7 +15522,7 @@
       <c r="A128" s="18">
         <v>1127</v>
       </c>
-      <c r="B128" s="32">
+      <c r="B128" s="27">
         <v>46065</v>
       </c>
       <c r="C128" s="18" t="s">
@@ -15563,7 +15563,7 @@
       <c r="A129" s="18">
         <v>1128</v>
       </c>
-      <c r="B129" s="32">
+      <c r="B129" s="27">
         <v>45755</v>
       </c>
       <c r="C129" s="18" t="s">
@@ -15604,7 +15604,7 @@
       <c r="A130" s="18">
         <v>1129</v>
       </c>
-      <c r="B130" s="32">
+      <c r="B130" s="27">
         <v>45891</v>
       </c>
       <c r="C130" s="18" t="s">
@@ -15645,7 +15645,7 @@
       <c r="A131" s="18">
         <v>1130</v>
       </c>
-      <c r="B131" s="32">
+      <c r="B131" s="27">
         <v>46013</v>
       </c>
       <c r="C131" s="18" t="s">
@@ -15686,7 +15686,7 @@
       <c r="A132" s="18">
         <v>1131</v>
       </c>
-      <c r="B132" s="32">
+      <c r="B132" s="27">
         <v>45739</v>
       </c>
       <c r="C132" s="18" t="s">
@@ -15727,7 +15727,7 @@
       <c r="A133" s="18">
         <v>1132</v>
       </c>
-      <c r="B133" s="32">
+      <c r="B133" s="27">
         <v>45879</v>
       </c>
       <c r="C133" s="18" t="s">
@@ -15768,7 +15768,7 @@
       <c r="A134" s="18">
         <v>1133</v>
       </c>
-      <c r="B134" s="32">
+      <c r="B134" s="27">
         <v>46036</v>
       </c>
       <c r="C134" s="18" t="s">
@@ -15809,7 +15809,7 @@
       <c r="A135" s="18">
         <v>1134</v>
       </c>
-      <c r="B135" s="32">
+      <c r="B135" s="27">
         <v>45947</v>
       </c>
       <c r="C135" s="18" t="s">
@@ -15850,7 +15850,7 @@
       <c r="A136" s="18">
         <v>1135</v>
       </c>
-      <c r="B136" s="32">
+      <c r="B136" s="27">
         <v>46192</v>
       </c>
       <c r="C136" s="18" t="s">
@@ -15891,7 +15891,7 @@
       <c r="A137" s="18">
         <v>1136</v>
       </c>
-      <c r="B137" s="32">
+      <c r="B137" s="27">
         <v>46017</v>
       </c>
       <c r="C137" s="18" t="s">
@@ -15932,7 +15932,7 @@
       <c r="A138" s="18">
         <v>1137</v>
       </c>
-      <c r="B138" s="32">
+      <c r="B138" s="27">
         <v>46163</v>
       </c>
       <c r="C138" s="18" t="s">
@@ -15973,7 +15973,7 @@
       <c r="A139" s="18">
         <v>1138</v>
       </c>
-      <c r="B139" s="32">
+      <c r="B139" s="27">
         <v>45783</v>
       </c>
       <c r="C139" s="18" t="s">
@@ -16014,7 +16014,7 @@
       <c r="A140" s="18">
         <v>1139</v>
       </c>
-      <c r="B140" s="32">
+      <c r="B140" s="27">
         <v>45731</v>
       </c>
       <c r="C140" s="18" t="s">
@@ -16055,7 +16055,7 @@
       <c r="A141" s="18">
         <v>1140</v>
       </c>
-      <c r="B141" s="32">
+      <c r="B141" s="27">
         <v>46026</v>
       </c>
       <c r="C141" s="18" t="s">
@@ -16096,7 +16096,7 @@
       <c r="A142" s="18">
         <v>1141</v>
       </c>
-      <c r="B142" s="32">
+      <c r="B142" s="27">
         <v>46156</v>
       </c>
       <c r="C142" s="18" t="s">
@@ -16137,7 +16137,7 @@
       <c r="A143" s="18">
         <v>1142</v>
       </c>
-      <c r="B143" s="32">
+      <c r="B143" s="27">
         <v>45962</v>
       </c>
       <c r="C143" s="18" t="s">
@@ -16178,7 +16178,7 @@
       <c r="A144" s="18">
         <v>1143</v>
       </c>
-      <c r="B144" s="32">
+      <c r="B144" s="27">
         <v>45677</v>
       </c>
       <c r="C144" s="18" t="s">
@@ -16219,7 +16219,7 @@
       <c r="A145" s="18">
         <v>1144</v>
       </c>
-      <c r="B145" s="32">
+      <c r="B145" s="27">
         <v>46132</v>
       </c>
       <c r="C145" s="18" t="s">
@@ -16260,7 +16260,7 @@
       <c r="A146" s="18">
         <v>1145</v>
       </c>
-      <c r="B146" s="32">
+      <c r="B146" s="27">
         <v>46028</v>
       </c>
       <c r="C146" s="18" t="s">
@@ -16301,7 +16301,7 @@
       <c r="A147" s="18">
         <v>1146</v>
       </c>
-      <c r="B147" s="32">
+      <c r="B147" s="27">
         <v>46030</v>
       </c>
       <c r="C147" s="18" t="s">
@@ -16342,7 +16342,7 @@
       <c r="A148" s="18">
         <v>1147</v>
       </c>
-      <c r="B148" s="32">
+      <c r="B148" s="27">
         <v>45673</v>
       </c>
       <c r="C148" s="18" t="s">
@@ -16383,7 +16383,7 @@
       <c r="A149" s="18">
         <v>1148</v>
       </c>
-      <c r="B149" s="32">
+      <c r="B149" s="27">
         <v>45964</v>
       </c>
       <c r="C149" s="18" t="s">
@@ -16424,7 +16424,7 @@
       <c r="A150" s="18">
         <v>1149</v>
       </c>
-      <c r="B150" s="32">
+      <c r="B150" s="27">
         <v>46195</v>
       </c>
       <c r="C150" s="18" t="s">
@@ -16465,7 +16465,7 @@
       <c r="A151" s="18">
         <v>1150</v>
       </c>
-      <c r="B151" s="32">
+      <c r="B151" s="27">
         <v>46039</v>
       </c>
       <c r="C151" s="18" t="s">
@@ -16506,7 +16506,7 @@
       <c r="A152" s="18">
         <v>1151</v>
       </c>
-      <c r="B152" s="32">
+      <c r="B152" s="27">
         <v>46197</v>
       </c>
       <c r="C152" s="18" t="s">
@@ -16547,7 +16547,7 @@
       <c r="A153" s="18">
         <v>1152</v>
       </c>
-      <c r="B153" s="32">
+      <c r="B153" s="27">
         <v>45811</v>
       </c>
       <c r="C153" s="18" t="s">
@@ -16588,7 +16588,7 @@
       <c r="A154" s="18">
         <v>1153</v>
       </c>
-      <c r="B154" s="32">
+      <c r="B154" s="27">
         <v>45756</v>
       </c>
       <c r="C154" s="18" t="s">
@@ -16629,7 +16629,7 @@
       <c r="A155" s="18">
         <v>1154</v>
       </c>
-      <c r="B155" s="32">
+      <c r="B155" s="27">
         <v>45714</v>
       </c>
       <c r="C155" s="18" t="s">
@@ -16670,7 +16670,7 @@
       <c r="A156" s="18">
         <v>1155</v>
       </c>
-      <c r="B156" s="32">
+      <c r="B156" s="27">
         <v>46172</v>
       </c>
       <c r="C156" s="18" t="s">
@@ -16711,7 +16711,7 @@
       <c r="A157" s="18">
         <v>1156</v>
       </c>
-      <c r="B157" s="32">
+      <c r="B157" s="27">
         <v>45875</v>
       </c>
       <c r="C157" s="18" t="s">
@@ -16752,7 +16752,7 @@
       <c r="A158" s="18">
         <v>1157</v>
       </c>
-      <c r="B158" s="32">
+      <c r="B158" s="27">
         <v>46006</v>
       </c>
       <c r="C158" s="18" t="s">
@@ -16793,7 +16793,7 @@
       <c r="A159" s="18">
         <v>1158</v>
       </c>
-      <c r="B159" s="32">
+      <c r="B159" s="27">
         <v>46131</v>
       </c>
       <c r="C159" s="18" t="s">
@@ -16834,7 +16834,7 @@
       <c r="A160" s="18">
         <v>1159</v>
       </c>
-      <c r="B160" s="32">
+      <c r="B160" s="27">
         <v>45768</v>
       </c>
       <c r="C160" s="18" t="s">
@@ -16875,7 +16875,7 @@
       <c r="A161" s="18">
         <v>1160</v>
       </c>
-      <c r="B161" s="32">
+      <c r="B161" s="27">
         <v>45680</v>
       </c>
       <c r="C161" s="18" t="s">
@@ -16916,7 +16916,7 @@
       <c r="A162" s="18">
         <v>1161</v>
       </c>
-      <c r="B162" s="32">
+      <c r="B162" s="27">
         <v>45753</v>
       </c>
       <c r="C162" s="18" t="s">
@@ -16957,7 +16957,7 @@
       <c r="A163" s="18">
         <v>1162</v>
       </c>
-      <c r="B163" s="32">
+      <c r="B163" s="27">
         <v>46060</v>
       </c>
       <c r="C163" s="18" t="s">
@@ -16998,7 +16998,7 @@
       <c r="A164" s="18">
         <v>1163</v>
       </c>
-      <c r="B164" s="32">
+      <c r="B164" s="27">
         <v>46009</v>
       </c>
       <c r="C164" s="18" t="s">
@@ -17039,7 +17039,7 @@
       <c r="A165" s="18">
         <v>1164</v>
       </c>
-      <c r="B165" s="32">
+      <c r="B165" s="27">
         <v>45711</v>
       </c>
       <c r="C165" s="18" t="s">
@@ -17080,7 +17080,7 @@
       <c r="A166" s="18">
         <v>1165</v>
       </c>
-      <c r="B166" s="32">
+      <c r="B166" s="27">
         <v>46058</v>
       </c>
       <c r="C166" s="18" t="s">
@@ -17121,7 +17121,7 @@
       <c r="A167" s="18">
         <v>1166</v>
       </c>
-      <c r="B167" s="32">
+      <c r="B167" s="27">
         <v>46074</v>
       </c>
       <c r="C167" s="18" t="s">
@@ -17162,7 +17162,7 @@
       <c r="A168" s="18">
         <v>1167</v>
       </c>
-      <c r="B168" s="32">
+      <c r="B168" s="27">
         <v>46160</v>
       </c>
       <c r="C168" s="18" t="s">
@@ -17203,7 +17203,7 @@
       <c r="A169" s="18">
         <v>1168</v>
       </c>
-      <c r="B169" s="32">
+      <c r="B169" s="27">
         <v>45846</v>
       </c>
       <c r="C169" s="18" t="s">
@@ -17244,7 +17244,7 @@
       <c r="A170" s="18">
         <v>1169</v>
       </c>
-      <c r="B170" s="32">
+      <c r="B170" s="27">
         <v>45916</v>
       </c>
       <c r="C170" s="18" t="s">
@@ -17285,7 +17285,7 @@
       <c r="A171" s="18">
         <v>1170</v>
       </c>
-      <c r="B171" s="32">
+      <c r="B171" s="27">
         <v>45703</v>
       </c>
       <c r="C171" s="18" t="s">
@@ -17326,7 +17326,7 @@
       <c r="A172" s="18">
         <v>1171</v>
       </c>
-      <c r="B172" s="32">
+      <c r="B172" s="27">
         <v>45748</v>
       </c>
       <c r="C172" s="18" t="s">
@@ -17367,7 +17367,7 @@
       <c r="A173" s="18">
         <v>1172</v>
       </c>
-      <c r="B173" s="32">
+      <c r="B173" s="27">
         <v>45852</v>
       </c>
       <c r="C173" s="18" t="s">
@@ -17408,7 +17408,7 @@
       <c r="A174" s="18">
         <v>1173</v>
       </c>
-      <c r="B174" s="32">
+      <c r="B174" s="27">
         <v>46000</v>
       </c>
       <c r="C174" s="18" t="s">
@@ -17449,7 +17449,7 @@
       <c r="A175" s="18">
         <v>1174</v>
       </c>
-      <c r="B175" s="32">
+      <c r="B175" s="27">
         <v>46171</v>
       </c>
       <c r="C175" s="18" t="s">
@@ -17490,7 +17490,7 @@
       <c r="A176" s="18">
         <v>1175</v>
       </c>
-      <c r="B176" s="32">
+      <c r="B176" s="27">
         <v>46071</v>
       </c>
       <c r="C176" s="18" t="s">
@@ -17531,7 +17531,7 @@
       <c r="A177" s="18">
         <v>1176</v>
       </c>
-      <c r="B177" s="32">
+      <c r="B177" s="27">
         <v>45780</v>
       </c>
       <c r="C177" s="18" t="s">
@@ -17572,7 +17572,7 @@
       <c r="A178" s="18">
         <v>1177</v>
       </c>
-      <c r="B178" s="32">
+      <c r="B178" s="27">
         <v>45701</v>
       </c>
       <c r="C178" s="18" t="s">
@@ -17613,7 +17613,7 @@
       <c r="A179" s="18">
         <v>1178</v>
       </c>
-      <c r="B179" s="32">
+      <c r="B179" s="27">
         <v>45977</v>
       </c>
       <c r="C179" s="18" t="s">
@@ -17654,7 +17654,7 @@
       <c r="A180" s="18">
         <v>1179</v>
       </c>
-      <c r="B180" s="32">
+      <c r="B180" s="27">
         <v>46038</v>
       </c>
       <c r="C180" s="18" t="s">
@@ -17695,7 +17695,7 @@
       <c r="A181" s="18">
         <v>1180</v>
       </c>
-      <c r="B181" s="32">
+      <c r="B181" s="27">
         <v>45805</v>
       </c>
       <c r="C181" s="18" t="s">
@@ -17736,7 +17736,7 @@
       <c r="A182" s="18">
         <v>1181</v>
       </c>
-      <c r="B182" s="32">
+      <c r="B182" s="27">
         <v>46131</v>
       </c>
       <c r="C182" s="18" t="s">
@@ -17777,7 +17777,7 @@
       <c r="A183" s="18">
         <v>1182</v>
       </c>
-      <c r="B183" s="32">
+      <c r="B183" s="27">
         <v>46111</v>
       </c>
       <c r="C183" s="18" t="s">
@@ -17818,7 +17818,7 @@
       <c r="A184" s="18">
         <v>1183</v>
       </c>
-      <c r="B184" s="32">
+      <c r="B184" s="27">
         <v>45767</v>
       </c>
       <c r="C184" s="18" t="s">
@@ -17859,7 +17859,7 @@
       <c r="A185" s="18">
         <v>1184</v>
       </c>
-      <c r="B185" s="32">
+      <c r="B185" s="27">
         <v>46167</v>
       </c>
       <c r="C185" s="18" t="s">
@@ -17900,7 +17900,7 @@
       <c r="A186" s="18">
         <v>1185</v>
       </c>
-      <c r="B186" s="32">
+      <c r="B186" s="27">
         <v>45826</v>
       </c>
       <c r="C186" s="18" t="s">
@@ -17941,7 +17941,7 @@
       <c r="A187" s="18">
         <v>1186</v>
       </c>
-      <c r="B187" s="32">
+      <c r="B187" s="27">
         <v>46155</v>
       </c>
       <c r="C187" s="18" t="s">
@@ -17982,7 +17982,7 @@
       <c r="A188" s="18">
         <v>1187</v>
       </c>
-      <c r="B188" s="32">
+      <c r="B188" s="27">
         <v>46194</v>
       </c>
       <c r="C188" s="18" t="s">
@@ -18023,7 +18023,7 @@
       <c r="A189" s="18">
         <v>1188</v>
       </c>
-      <c r="B189" s="32">
+      <c r="B189" s="27">
         <v>45729</v>
       </c>
       <c r="C189" s="18" t="s">
@@ -18064,7 +18064,7 @@
       <c r="A190" s="18">
         <v>1189</v>
       </c>
-      <c r="B190" s="32">
+      <c r="B190" s="27">
         <v>45923</v>
       </c>
       <c r="C190" s="18" t="s">
@@ -18105,7 +18105,7 @@
       <c r="A191" s="18">
         <v>1190</v>
       </c>
-      <c r="B191" s="32">
+      <c r="B191" s="27">
         <v>46172</v>
       </c>
       <c r="C191" s="18" t="s">
@@ -18146,7 +18146,7 @@
       <c r="A192" s="18">
         <v>1191</v>
       </c>
-      <c r="B192" s="32">
+      <c r="B192" s="27">
         <v>45946</v>
       </c>
       <c r="C192" s="18" t="s">
@@ -18187,7 +18187,7 @@
       <c r="A193" s="18">
         <v>1192</v>
       </c>
-      <c r="B193" s="32">
+      <c r="B193" s="27">
         <v>46038</v>
       </c>
       <c r="C193" s="18" t="s">
@@ -18228,7 +18228,7 @@
       <c r="A194" s="18">
         <v>1193</v>
       </c>
-      <c r="B194" s="32">
+      <c r="B194" s="27">
         <v>45869</v>
       </c>
       <c r="C194" s="18" t="s">
@@ -18269,7 +18269,7 @@
       <c r="A195" s="18">
         <v>1194</v>
       </c>
-      <c r="B195" s="32">
+      <c r="B195" s="27">
         <v>46158</v>
       </c>
       <c r="C195" s="18" t="s">
@@ -18310,7 +18310,7 @@
       <c r="A196" s="18">
         <v>1195</v>
       </c>
-      <c r="B196" s="32">
+      <c r="B196" s="27">
         <v>46170</v>
       </c>
       <c r="C196" s="18" t="s">
@@ -18351,7 +18351,7 @@
       <c r="A197" s="18">
         <v>1196</v>
       </c>
-      <c r="B197" s="32">
+      <c r="B197" s="27">
         <v>46064</v>
       </c>
       <c r="C197" s="18" t="s">
@@ -18392,7 +18392,7 @@
       <c r="A198" s="18">
         <v>1197</v>
       </c>
-      <c r="B198" s="32">
+      <c r="B198" s="27">
         <v>45925</v>
       </c>
       <c r="C198" s="18" t="s">
@@ -18433,7 +18433,7 @@
       <c r="A199" s="18">
         <v>1198</v>
       </c>
-      <c r="B199" s="32">
+      <c r="B199" s="27">
         <v>45775</v>
       </c>
       <c r="C199" s="18" t="s">
@@ -18474,7 +18474,7 @@
       <c r="A200" s="18">
         <v>1199</v>
       </c>
-      <c r="B200" s="32">
+      <c r="B200" s="27">
         <v>45919</v>
       </c>
       <c r="C200" s="18" t="s">
@@ -18515,7 +18515,7 @@
       <c r="A201" s="18">
         <v>1200</v>
       </c>
-      <c r="B201" s="32">
+      <c r="B201" s="27">
         <v>45978</v>
       </c>
       <c r="C201" s="18" t="s">
@@ -18556,7 +18556,7 @@
       <c r="A202" s="18">
         <v>1201</v>
       </c>
-      <c r="B202" s="32">
+      <c r="B202" s="27">
         <v>45852</v>
       </c>
       <c r="C202" s="18" t="s">
@@ -18597,7 +18597,7 @@
       <c r="A203" s="18">
         <v>1202</v>
       </c>
-      <c r="B203" s="32">
+      <c r="B203" s="27">
         <v>45788</v>
       </c>
       <c r="C203" s="18" t="s">
@@ -18638,7 +18638,7 @@
       <c r="A204" s="18">
         <v>1203</v>
       </c>
-      <c r="B204" s="32">
+      <c r="B204" s="27">
         <v>45843</v>
       </c>
       <c r="C204" s="18" t="s">
@@ -18679,7 +18679,7 @@
       <c r="A205" s="18">
         <v>1204</v>
       </c>
-      <c r="B205" s="32">
+      <c r="B205" s="27">
         <v>46133</v>
       </c>
       <c r="C205" s="18" t="s">
@@ -18720,7 +18720,7 @@
       <c r="A206" s="18">
         <v>1205</v>
       </c>
-      <c r="B206" s="32">
+      <c r="B206" s="27">
         <v>46031</v>
       </c>
       <c r="C206" s="18" t="s">
@@ -18761,7 +18761,7 @@
       <c r="A207" s="18">
         <v>1206</v>
       </c>
-      <c r="B207" s="32">
+      <c r="B207" s="27">
         <v>45917</v>
       </c>
       <c r="C207" s="18" t="s">
@@ -18802,7 +18802,7 @@
       <c r="A208" s="18">
         <v>1207</v>
       </c>
-      <c r="B208" s="32">
+      <c r="B208" s="27">
         <v>46181</v>
       </c>
       <c r="C208" s="18" t="s">
@@ -18843,7 +18843,7 @@
       <c r="A209" s="18">
         <v>1208</v>
       </c>
-      <c r="B209" s="32">
+      <c r="B209" s="27">
         <v>46160</v>
       </c>
       <c r="C209" s="18" t="s">
@@ -18884,7 +18884,7 @@
       <c r="A210" s="18">
         <v>1209</v>
       </c>
-      <c r="B210" s="32">
+      <c r="B210" s="27">
         <v>45994</v>
       </c>
       <c r="C210" s="18" t="s">
@@ -18925,7 +18925,7 @@
       <c r="A211" s="18">
         <v>1210</v>
       </c>
-      <c r="B211" s="32">
+      <c r="B211" s="27">
         <v>45663</v>
       </c>
       <c r="C211" s="18" t="s">
@@ -18966,7 +18966,7 @@
       <c r="A212" s="18">
         <v>1211</v>
       </c>
-      <c r="B212" s="32">
+      <c r="B212" s="27">
         <v>46053</v>
       </c>
       <c r="C212" s="18" t="s">
@@ -19007,7 +19007,7 @@
       <c r="A213" s="18">
         <v>1212</v>
       </c>
-      <c r="B213" s="32">
+      <c r="B213" s="27">
         <v>45834</v>
       </c>
       <c r="C213" s="18" t="s">
@@ -19048,7 +19048,7 @@
       <c r="A214" s="18">
         <v>1213</v>
       </c>
-      <c r="B214" s="32">
+      <c r="B214" s="27">
         <v>46049</v>
       </c>
       <c r="C214" s="18" t="s">
@@ -19089,7 +19089,7 @@
       <c r="A215" s="18">
         <v>1214</v>
       </c>
-      <c r="B215" s="32">
+      <c r="B215" s="27">
         <v>45914</v>
       </c>
       <c r="C215" s="18" t="s">
@@ -19130,7 +19130,7 @@
       <c r="A216" s="18">
         <v>1215</v>
       </c>
-      <c r="B216" s="32">
+      <c r="B216" s="27">
         <v>45770</v>
       </c>
       <c r="C216" s="18" t="s">
@@ -19171,7 +19171,7 @@
       <c r="A217" s="18">
         <v>1216</v>
       </c>
-      <c r="B217" s="32">
+      <c r="B217" s="27">
         <v>45764</v>
       </c>
       <c r="C217" s="18" t="s">
@@ -19212,7 +19212,7 @@
       <c r="A218" s="18">
         <v>1217</v>
       </c>
-      <c r="B218" s="32">
+      <c r="B218" s="27">
         <v>46083</v>
       </c>
       <c r="C218" s="18" t="s">
@@ -19253,7 +19253,7 @@
       <c r="A219" s="18">
         <v>1218</v>
       </c>
-      <c r="B219" s="32">
+      <c r="B219" s="27">
         <v>45889</v>
       </c>
       <c r="C219" s="18" t="s">
@@ -19294,7 +19294,7 @@
       <c r="A220" s="18">
         <v>1219</v>
       </c>
-      <c r="B220" s="32">
+      <c r="B220" s="27">
         <v>45866</v>
       </c>
       <c r="C220" s="18" t="s">
@@ -19335,7 +19335,7 @@
       <c r="A221" s="18">
         <v>1220</v>
       </c>
-      <c r="B221" s="32">
+      <c r="B221" s="27">
         <v>45691</v>
       </c>
       <c r="C221" s="18" t="s">
@@ -19376,7 +19376,7 @@
       <c r="A222" s="18">
         <v>1221</v>
       </c>
-      <c r="B222" s="32">
+      <c r="B222" s="27">
         <v>45684</v>
       </c>
       <c r="C222" s="18" t="s">
@@ -19417,7 +19417,7 @@
       <c r="A223" s="18">
         <v>1222</v>
       </c>
-      <c r="B223" s="32">
+      <c r="B223" s="27">
         <v>45672</v>
       </c>
       <c r="C223" s="18" t="s">
@@ -19458,7 +19458,7 @@
       <c r="A224" s="18">
         <v>1223</v>
       </c>
-      <c r="B224" s="32">
+      <c r="B224" s="27">
         <v>45915</v>
       </c>
       <c r="C224" s="18" t="s">
@@ -19499,7 +19499,7 @@
       <c r="A225" s="18">
         <v>1224</v>
       </c>
-      <c r="B225" s="32">
+      <c r="B225" s="27">
         <v>46027</v>
       </c>
       <c r="C225" s="18" t="s">
@@ -19540,7 +19540,7 @@
       <c r="A226" s="18">
         <v>1225</v>
       </c>
-      <c r="B226" s="32">
+      <c r="B226" s="27">
         <v>45992</v>
       </c>
       <c r="C226" s="18" t="s">
@@ -19581,7 +19581,7 @@
       <c r="A227" s="18">
         <v>1226</v>
       </c>
-      <c r="B227" s="32">
+      <c r="B227" s="27">
         <v>46083</v>
       </c>
       <c r="C227" s="18" t="s">
@@ -19622,7 +19622,7 @@
       <c r="A228" s="18">
         <v>1227</v>
       </c>
-      <c r="B228" s="32">
+      <c r="B228" s="27">
         <v>46072</v>
       </c>
       <c r="C228" s="18" t="s">
@@ -19663,7 +19663,7 @@
       <c r="A229" s="18">
         <v>1228</v>
       </c>
-      <c r="B229" s="32">
+      <c r="B229" s="27">
         <v>45991</v>
       </c>
       <c r="C229" s="18" t="s">
@@ -19704,7 +19704,7 @@
       <c r="A230" s="18">
         <v>1229</v>
       </c>
-      <c r="B230" s="32">
+      <c r="B230" s="27">
         <v>45951</v>
       </c>
       <c r="C230" s="18" t="s">
@@ -19745,7 +19745,7 @@
       <c r="A231" s="18">
         <v>1230</v>
       </c>
-      <c r="B231" s="32">
+      <c r="B231" s="27">
         <v>46149</v>
       </c>
       <c r="C231" s="18" t="s">
@@ -19786,7 +19786,7 @@
       <c r="A232" s="18">
         <v>1231</v>
       </c>
-      <c r="B232" s="32">
+      <c r="B232" s="27">
         <v>45847</v>
       </c>
       <c r="C232" s="18" t="s">
@@ -19827,7 +19827,7 @@
       <c r="A233" s="18">
         <v>1232</v>
       </c>
-      <c r="B233" s="32">
+      <c r="B233" s="27">
         <v>45785</v>
       </c>
       <c r="C233" s="18" t="s">
@@ -19868,7 +19868,7 @@
       <c r="A234" s="18">
         <v>1233</v>
       </c>
-      <c r="B234" s="32">
+      <c r="B234" s="27">
         <v>45987</v>
       </c>
       <c r="C234" s="18" t="s">
@@ -19909,7 +19909,7 @@
       <c r="A235" s="18">
         <v>1234</v>
       </c>
-      <c r="B235" s="32">
+      <c r="B235" s="27">
         <v>45959</v>
       </c>
       <c r="C235" s="18" t="s">
@@ -19950,7 +19950,7 @@
       <c r="A236" s="18">
         <v>1235</v>
       </c>
-      <c r="B236" s="32">
+      <c r="B236" s="27">
         <v>45815</v>
       </c>
       <c r="C236" s="18" t="s">
@@ -19991,7 +19991,7 @@
       <c r="A237" s="18">
         <v>1236</v>
       </c>
-      <c r="B237" s="32">
+      <c r="B237" s="27">
         <v>45935</v>
       </c>
       <c r="C237" s="18" t="s">
@@ -20032,7 +20032,7 @@
       <c r="A238" s="18">
         <v>1237</v>
       </c>
-      <c r="B238" s="32">
+      <c r="B238" s="27">
         <v>45789</v>
       </c>
       <c r="C238" s="18" t="s">
@@ -20073,7 +20073,7 @@
       <c r="A239" s="18">
         <v>1238</v>
       </c>
-      <c r="B239" s="32">
+      <c r="B239" s="27">
         <v>45798</v>
       </c>
       <c r="C239" s="18" t="s">
@@ -20114,7 +20114,7 @@
       <c r="A240" s="18">
         <v>1239</v>
       </c>
-      <c r="B240" s="32">
+      <c r="B240" s="27">
         <v>46090</v>
       </c>
       <c r="C240" s="18" t="s">
@@ -20155,7 +20155,7 @@
       <c r="A241" s="18">
         <v>1240</v>
       </c>
-      <c r="B241" s="32">
+      <c r="B241" s="27">
         <v>45850</v>
       </c>
       <c r="C241" s="18" t="s">
@@ -20196,7 +20196,7 @@
       <c r="A242" s="18">
         <v>1241</v>
       </c>
-      <c r="B242" s="32">
+      <c r="B242" s="27">
         <v>46167</v>
       </c>
       <c r="C242" s="18" t="s">
@@ -20237,7 +20237,7 @@
       <c r="A243" s="18">
         <v>1242</v>
       </c>
-      <c r="B243" s="32">
+      <c r="B243" s="27">
         <v>46188</v>
       </c>
       <c r="C243" s="18" t="s">
@@ -20278,7 +20278,7 @@
       <c r="A244" s="18">
         <v>1243</v>
       </c>
-      <c r="B244" s="32">
+      <c r="B244" s="27">
         <v>45731</v>
       </c>
       <c r="C244" s="18" t="s">
@@ -20319,7 +20319,7 @@
       <c r="A245" s="18">
         <v>1244</v>
       </c>
-      <c r="B245" s="32">
+      <c r="B245" s="27">
         <v>46146</v>
       </c>
       <c r="C245" s="18" t="s">
@@ -20360,7 +20360,7 @@
       <c r="A246" s="18">
         <v>1245</v>
       </c>
-      <c r="B246" s="32">
+      <c r="B246" s="27">
         <v>45822</v>
       </c>
       <c r="C246" s="18" t="s">
@@ -20401,7 +20401,7 @@
       <c r="A247" s="18">
         <v>1246</v>
       </c>
-      <c r="B247" s="32">
+      <c r="B247" s="27">
         <v>45805</v>
       </c>
       <c r="C247" s="18" t="s">
@@ -20442,7 +20442,7 @@
       <c r="A248" s="18">
         <v>1247</v>
       </c>
-      <c r="B248" s="32">
+      <c r="B248" s="27">
         <v>46117</v>
       </c>
       <c r="C248" s="18" t="s">
@@ -20483,7 +20483,7 @@
       <c r="A249" s="18">
         <v>1248</v>
       </c>
-      <c r="B249" s="32">
+      <c r="B249" s="27">
         <v>46066</v>
       </c>
       <c r="C249" s="18" t="s">
@@ -20524,7 +20524,7 @@
       <c r="A250" s="18">
         <v>1249</v>
       </c>
-      <c r="B250" s="32">
+      <c r="B250" s="27">
         <v>45927</v>
       </c>
       <c r="C250" s="18" t="s">
@@ -20565,7 +20565,7 @@
       <c r="A251" s="18">
         <v>1250</v>
       </c>
-      <c r="B251" s="32">
+      <c r="B251" s="27">
         <v>45878</v>
       </c>
       <c r="C251" s="18" t="s">
@@ -20606,7 +20606,7 @@
       <c r="A252" s="18">
         <v>1251</v>
       </c>
-      <c r="B252" s="32">
+      <c r="B252" s="27">
         <v>46190</v>
       </c>
       <c r="C252" s="18" t="s">
@@ -20647,7 +20647,7 @@
       <c r="A253" s="18">
         <v>1252</v>
       </c>
-      <c r="B253" s="32">
+      <c r="B253" s="27">
         <v>46014</v>
       </c>
       <c r="C253" s="18" t="s">
@@ -20688,7 +20688,7 @@
       <c r="A254" s="18">
         <v>1253</v>
       </c>
-      <c r="B254" s="32">
+      <c r="B254" s="27">
         <v>45996</v>
       </c>
       <c r="C254" s="18" t="s">
@@ -20729,7 +20729,7 @@
       <c r="A255" s="18">
         <v>1254</v>
       </c>
-      <c r="B255" s="32">
+      <c r="B255" s="27">
         <v>45947</v>
       </c>
       <c r="C255" s="18" t="s">
@@ -20770,7 +20770,7 @@
       <c r="A256" s="18">
         <v>1255</v>
       </c>
-      <c r="B256" s="32">
+      <c r="B256" s="27">
         <v>45749</v>
       </c>
       <c r="C256" s="18" t="s">
@@ -20811,7 +20811,7 @@
       <c r="A257" s="18">
         <v>1256</v>
       </c>
-      <c r="B257" s="32">
+      <c r="B257" s="27">
         <v>46095</v>
       </c>
       <c r="C257" s="18" t="s">
@@ -20852,7 +20852,7 @@
       <c r="A258" s="18">
         <v>1257</v>
       </c>
-      <c r="B258" s="32">
+      <c r="B258" s="27">
         <v>45787</v>
       </c>
       <c r="C258" s="18" t="s">
@@ -20893,7 +20893,7 @@
       <c r="A259" s="18">
         <v>1258</v>
       </c>
-      <c r="B259" s="32">
+      <c r="B259" s="27">
         <v>46094</v>
       </c>
       <c r="C259" s="18" t="s">
@@ -20934,7 +20934,7 @@
       <c r="A260" s="18">
         <v>1259</v>
       </c>
-      <c r="B260" s="32">
+      <c r="B260" s="27">
         <v>46100</v>
       </c>
       <c r="C260" s="18" t="s">
@@ -20975,7 +20975,7 @@
       <c r="A261" s="18">
         <v>1260</v>
       </c>
-      <c r="B261" s="32">
+      <c r="B261" s="27">
         <v>45899</v>
       </c>
       <c r="C261" s="18" t="s">
@@ -21016,7 +21016,7 @@
       <c r="A262" s="18">
         <v>1261</v>
       </c>
-      <c r="B262" s="32">
+      <c r="B262" s="27">
         <v>46145</v>
       </c>
       <c r="C262" s="18" t="s">
@@ -21057,7 +21057,7 @@
       <c r="A263" s="18">
         <v>1262</v>
       </c>
-      <c r="B263" s="32">
+      <c r="B263" s="27">
         <v>45807</v>
       </c>
       <c r="C263" s="18" t="s">
@@ -21098,7 +21098,7 @@
       <c r="A264" s="18">
         <v>1263</v>
       </c>
-      <c r="B264" s="32">
+      <c r="B264" s="27">
         <v>46011</v>
       </c>
       <c r="C264" s="18" t="s">
@@ -21139,7 +21139,7 @@
       <c r="A265" s="18">
         <v>1264</v>
       </c>
-      <c r="B265" s="32">
+      <c r="B265" s="27">
         <v>46032</v>
       </c>
       <c r="C265" s="18" t="s">
@@ -21180,7 +21180,7 @@
       <c r="A266" s="18">
         <v>1265</v>
       </c>
-      <c r="B266" s="32">
+      <c r="B266" s="27">
         <v>45812</v>
       </c>
       <c r="C266" s="18" t="s">
@@ -21221,7 +21221,7 @@
       <c r="A267" s="18">
         <v>1266</v>
       </c>
-      <c r="B267" s="32">
+      <c r="B267" s="27">
         <v>45911</v>
       </c>
       <c r="C267" s="18" t="s">
@@ -21262,7 +21262,7 @@
       <c r="A268" s="18">
         <v>1267</v>
       </c>
-      <c r="B268" s="32">
+      <c r="B268" s="27">
         <v>45924</v>
       </c>
       <c r="C268" s="18" t="s">
@@ -21303,7 +21303,7 @@
       <c r="A269" s="18">
         <v>1268</v>
       </c>
-      <c r="B269" s="32">
+      <c r="B269" s="27">
         <v>46094</v>
       </c>
       <c r="C269" s="18" t="s">
@@ -21344,7 +21344,7 @@
       <c r="A270" s="18">
         <v>1269</v>
       </c>
-      <c r="B270" s="32">
+      <c r="B270" s="27">
         <v>45804</v>
       </c>
       <c r="C270" s="18" t="s">
@@ -21385,7 +21385,7 @@
       <c r="A271" s="18">
         <v>1270</v>
       </c>
-      <c r="B271" s="32">
+      <c r="B271" s="27">
         <v>45679</v>
       </c>
       <c r="C271" s="18" t="s">
@@ -21426,7 +21426,7 @@
       <c r="A272" s="18">
         <v>1271</v>
       </c>
-      <c r="B272" s="32">
+      <c r="B272" s="27">
         <v>46172</v>
       </c>
       <c r="C272" s="18" t="s">
@@ -21467,7 +21467,7 @@
       <c r="A273" s="18">
         <v>1272</v>
       </c>
-      <c r="B273" s="32">
+      <c r="B273" s="27">
         <v>45715</v>
       </c>
       <c r="C273" s="18" t="s">
@@ -21508,7 +21508,7 @@
       <c r="A274" s="18">
         <v>1273</v>
       </c>
-      <c r="B274" s="32">
+      <c r="B274" s="27">
         <v>45781</v>
       </c>
       <c r="C274" s="18" t="s">
@@ -21549,7 +21549,7 @@
       <c r="A275" s="18">
         <v>1274</v>
       </c>
-      <c r="B275" s="32">
+      <c r="B275" s="27">
         <v>45688</v>
       </c>
       <c r="C275" s="18" t="s">
@@ -21590,7 +21590,7 @@
       <c r="A276" s="18">
         <v>1275</v>
       </c>
-      <c r="B276" s="32">
+      <c r="B276" s="27">
         <v>46187</v>
       </c>
       <c r="C276" s="18" t="s">
@@ -21631,7 +21631,7 @@
       <c r="A277" s="18">
         <v>1276</v>
       </c>
-      <c r="B277" s="32">
+      <c r="B277" s="27">
         <v>45658</v>
       </c>
       <c r="C277" s="18" t="s">
@@ -21672,7 +21672,7 @@
       <c r="A278" s="18">
         <v>1277</v>
       </c>
-      <c r="B278" s="32">
+      <c r="B278" s="27">
         <v>46103</v>
       </c>
       <c r="C278" s="18" t="s">
@@ -21713,7 +21713,7 @@
       <c r="A279" s="18">
         <v>1278</v>
       </c>
-      <c r="B279" s="32">
+      <c r="B279" s="27">
         <v>46036</v>
       </c>
       <c r="C279" s="18" t="s">
@@ -21754,7 +21754,7 @@
       <c r="A280" s="18">
         <v>1279</v>
       </c>
-      <c r="B280" s="32">
+      <c r="B280" s="27">
         <v>46003</v>
       </c>
       <c r="C280" s="18" t="s">
@@ -21795,7 +21795,7 @@
       <c r="A281" s="18">
         <v>1280</v>
       </c>
-      <c r="B281" s="32">
+      <c r="B281" s="27">
         <v>45973</v>
       </c>
       <c r="C281" s="18" t="s">
@@ -21836,7 +21836,7 @@
       <c r="A282" s="18">
         <v>1281</v>
       </c>
-      <c r="B282" s="32">
+      <c r="B282" s="27">
         <v>45990</v>
       </c>
       <c r="C282" s="18" t="s">
@@ -21877,7 +21877,7 @@
       <c r="A283" s="18">
         <v>1282</v>
       </c>
-      <c r="B283" s="32">
+      <c r="B283" s="27">
         <v>45949</v>
       </c>
       <c r="C283" s="18" t="s">
@@ -21918,7 +21918,7 @@
       <c r="A284" s="18">
         <v>1283</v>
       </c>
-      <c r="B284" s="32">
+      <c r="B284" s="27">
         <v>46053</v>
       </c>
       <c r="C284" s="18" t="s">
@@ -21959,7 +21959,7 @@
       <c r="A285" s="18">
         <v>1284</v>
       </c>
-      <c r="B285" s="32">
+      <c r="B285" s="27">
         <v>45750</v>
       </c>
       <c r="C285" s="18" t="s">
@@ -22000,7 +22000,7 @@
       <c r="A286" s="18">
         <v>1285</v>
       </c>
-      <c r="B286" s="32">
+      <c r="B286" s="27">
         <v>45875</v>
       </c>
       <c r="C286" s="18" t="s">
@@ -22041,7 +22041,7 @@
       <c r="A287" s="18">
         <v>1286</v>
       </c>
-      <c r="B287" s="32">
+      <c r="B287" s="27">
         <v>45711</v>
       </c>
       <c r="C287" s="18" t="s">
@@ -22082,7 +22082,7 @@
       <c r="A288" s="18">
         <v>1287</v>
       </c>
-      <c r="B288" s="32">
+      <c r="B288" s="27">
         <v>45871</v>
       </c>
       <c r="C288" s="18" t="s">
@@ -22123,7 +22123,7 @@
       <c r="A289" s="18">
         <v>1288</v>
       </c>
-      <c r="B289" s="32">
+      <c r="B289" s="27">
         <v>45742</v>
       </c>
       <c r="C289" s="18" t="s">
@@ -22164,7 +22164,7 @@
       <c r="A290" s="18">
         <v>1289</v>
       </c>
-      <c r="B290" s="32">
+      <c r="B290" s="27">
         <v>45962</v>
       </c>
       <c r="C290" s="18" t="s">
@@ -22205,7 +22205,7 @@
       <c r="A291" s="18">
         <v>1290</v>
       </c>
-      <c r="B291" s="32">
+      <c r="B291" s="27">
         <v>46150</v>
       </c>
       <c r="C291" s="18" t="s">
@@ -22246,7 +22246,7 @@
       <c r="A292" s="18">
         <v>1291</v>
       </c>
-      <c r="B292" s="32">
+      <c r="B292" s="27">
         <v>45941</v>
       </c>
       <c r="C292" s="18" t="s">
@@ -22287,7 +22287,7 @@
       <c r="A293" s="18">
         <v>1292</v>
       </c>
-      <c r="B293" s="32">
+      <c r="B293" s="27">
         <v>45722</v>
       </c>
       <c r="C293" s="18" t="s">
@@ -22328,7 +22328,7 @@
       <c r="A294" s="18">
         <v>1293</v>
       </c>
-      <c r="B294" s="32">
+      <c r="B294" s="27">
         <v>46099</v>
       </c>
       <c r="C294" s="18" t="s">
@@ -22369,7 +22369,7 @@
       <c r="A295" s="18">
         <v>1294</v>
       </c>
-      <c r="B295" s="32">
+      <c r="B295" s="27">
         <v>46035</v>
       </c>
       <c r="C295" s="18" t="s">
@@ -22410,7 +22410,7 @@
       <c r="A296" s="18">
         <v>1295</v>
       </c>
-      <c r="B296" s="32">
+      <c r="B296" s="27">
         <v>46178</v>
       </c>
       <c r="C296" s="18" t="s">
@@ -22451,7 +22451,7 @@
       <c r="A297" s="18">
         <v>1296</v>
       </c>
-      <c r="B297" s="32">
+      <c r="B297" s="27">
         <v>45939</v>
       </c>
       <c r="C297" s="18" t="s">
@@ -22492,7 +22492,7 @@
       <c r="A298" s="18">
         <v>1297</v>
       </c>
-      <c r="B298" s="32">
+      <c r="B298" s="27">
         <v>46090</v>
       </c>
       <c r="C298" s="18" t="s">
@@ -22533,7 +22533,7 @@
       <c r="A299" s="18">
         <v>1298</v>
       </c>
-      <c r="B299" s="32">
+      <c r="B299" s="27">
         <v>45861</v>
       </c>
       <c r="C299" s="18" t="s">
@@ -22574,7 +22574,7 @@
       <c r="A300" s="18">
         <v>1299</v>
       </c>
-      <c r="B300" s="32">
+      <c r="B300" s="27">
         <v>45707</v>
       </c>
       <c r="C300" s="18" t="s">
@@ -22615,7 +22615,7 @@
       <c r="A301" s="18">
         <v>1300</v>
       </c>
-      <c r="B301" s="32">
+      <c r="B301" s="27">
         <v>45720</v>
       </c>
       <c r="C301" s="18" t="s">
@@ -72182,7 +72182,7 @@
     <col min="2" max="2" width="19.6328125" style="10" customWidth="1"/>
     <col min="3" max="4" width="13.1796875" style="10" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="19.453125" style="10" customWidth="1"/>
-    <col min="6" max="6" width="14.453125" style="10" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.26953125" style="10" customWidth="1"/>
     <col min="7" max="7" width="4.453125" style="10" customWidth="1"/>
     <col min="8" max="8" width="11.08984375" style="10" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.6328125" style="10" bestFit="1" customWidth="1"/>
@@ -72206,22 +72206,22 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:12" ht="23.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="30" t="s">
+      <c r="A2" s="31" t="s">
         <v>124</v>
       </c>
-      <c r="B2" s="28"/>
-      <c r="E2" s="30" t="s">
+      <c r="B2" s="29"/>
+      <c r="E2" s="31" t="s">
         <v>125</v>
       </c>
-      <c r="F2" s="28"/>
-      <c r="H2" s="30" t="s">
+      <c r="F2" s="29"/>
+      <c r="H2" s="31" t="s">
         <v>126</v>
       </c>
-      <c r="I2" s="28"/>
-      <c r="K2" s="30" t="s">
+      <c r="I2" s="29"/>
+      <c r="K2" s="31" t="s">
         <v>127</v>
       </c>
-      <c r="L2" s="28"/>
+      <c r="L2" s="29"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="19" t="s">
@@ -72390,22 +72390,22 @@
       </c>
     </row>
     <row r="12" spans="1:12" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="27" t="s">
+      <c r="A12" s="28" t="s">
         <v>134</v>
       </c>
-      <c r="B12" s="28"/>
-      <c r="E12" s="31" t="s">
+      <c r="B12" s="29"/>
+      <c r="E12" s="32" t="s">
         <v>135</v>
       </c>
-      <c r="F12" s="28"/>
-      <c r="H12" s="27" t="s">
+      <c r="F12" s="29"/>
+      <c r="H12" s="28" t="s">
         <v>136</v>
       </c>
-      <c r="I12" s="28"/>
-      <c r="K12" s="27" t="s">
+      <c r="I12" s="29"/>
+      <c r="K12" s="28" t="s">
         <v>137</v>
       </c>
-      <c r="L12" s="28"/>
+      <c r="L12" s="29"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13" s="9" t="s">
@@ -72560,10 +72560,10 @@
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A20" s="27" t="s">
+      <c r="A20" s="28" t="s">
         <v>155</v>
       </c>
-      <c r="B20" s="28"/>
+      <c r="B20" s="29"/>
       <c r="H20" s="8" t="s">
         <v>156</v>
       </c>
@@ -72578,20 +72578,20 @@
       <c r="B21" t="s">
         <v>157</v>
       </c>
-      <c r="E21" s="27" t="s">
+      <c r="E21" s="28" t="s">
         <v>158</v>
       </c>
-      <c r="F21" s="28"/>
+      <c r="F21" s="29"/>
       <c r="H21" s="8" t="s">
         <v>159</v>
       </c>
       <c r="I21" s="13">
         <v>75341.539999999994</v>
       </c>
-      <c r="K21" s="27" t="s">
+      <c r="K21" s="28" t="s">
         <v>160</v>
       </c>
-      <c r="L21" s="28"/>
+      <c r="L21" s="29"/>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A22" s="8" t="s">
@@ -72770,21 +72770,21 @@
       </c>
     </row>
     <row r="34" spans="1:13" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="27" t="s">
+      <c r="A34" s="28" t="s">
         <v>166</v>
       </c>
-      <c r="B34" s="28"/>
-      <c r="C34" s="28"/>
-      <c r="D34" s="28"/>
-      <c r="E34" s="28"/>
-      <c r="H34" s="27" t="s">
+      <c r="B34" s="29"/>
+      <c r="C34" s="29"/>
+      <c r="D34" s="29"/>
+      <c r="E34" s="29"/>
+      <c r="H34" s="28" t="s">
         <v>167</v>
       </c>
-      <c r="I34" s="27"/>
-      <c r="J34" s="27"/>
-      <c r="K34" s="27"/>
-      <c r="L34" s="27"/>
-      <c r="M34" s="27"/>
+      <c r="I34" s="28"/>
+      <c r="J34" s="28"/>
+      <c r="K34" s="28"/>
+      <c r="L34" s="28"/>
+      <c r="M34" s="28"/>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A35" s="9" t="s">
@@ -72993,14 +72993,14 @@
       </c>
     </row>
     <row r="47" spans="1:13" ht="23" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="27" t="s">
+      <c r="A47" s="28" t="s">
         <v>169</v>
       </c>
-      <c r="B47" s="29"/>
-      <c r="C47" s="29"/>
-      <c r="D47" s="29"/>
-      <c r="E47" s="29"/>
-      <c r="F47" s="29"/>
+      <c r="B47" s="30"/>
+      <c r="C47" s="30"/>
+      <c r="D47" s="30"/>
+      <c r="E47" s="30"/>
+      <c r="F47" s="30"/>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A48" s="9" t="s">
